--- a/experiment_results/wedos_grid/rtt_bursts_S4_atk10pct_wu400000_stage1a_rep1.xlsx
+++ b/experiment_results/wedos_grid/rtt_bursts_S4_atk10pct_wu400000_stage1a_rep1.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>184864</t>
+          <t>132093</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>388180</t>
+          <t>256876</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>545575</t>
+          <t>289488</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>722366</t>
+          <t>433667</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1061112</t>
+          <t>628234</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1414136</t>
+          <t>786691</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1581606</t>
+          <t>795704</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1569252</t>
+          <t>774337</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1547886</t>
+          <t>774337</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
